--- a/action/T_HT00.xlsx
+++ b/action/T_HT00.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sports\FUT_STATS_APP\action\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBEDE978-E779-4725-AE92-9F968344942F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83EF0B2E-874E-418F-91CA-F5739F78253B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LAY DRAW HT" sheetId="1" r:id="rId1"/>
@@ -2662,6 +2662,9 @@
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B27" s="16">
+        <v>26</v>
+      </c>
       <c r="C27" s="5">
         <v>46086</v>
       </c>
@@ -2704,6 +2707,9 @@
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B28" s="16">
+        <v>27</v>
+      </c>
       <c r="C28" s="5">
         <v>46086</v>
       </c>
@@ -2719,7 +2725,7 @@
       <c r="G28" s="14">
         <v>2</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H28" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2747,6 +2753,9 @@
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B29" s="16">
+        <v>28</v>
+      </c>
       <c r="C29" s="5">
         <v>46086</v>
       </c>
@@ -2762,7 +2771,7 @@
       <c r="G29" s="14">
         <v>0</v>
       </c>
-      <c r="H29" s="14">
+      <c r="H29" s="16">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
